--- a/LISTEN/Script/21_7/21_7.xlsx
+++ b/LISTEN/Script/21_7/21_7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\21_7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD53D98E-164B-45D2-8FBF-10BA19FBA90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A57A748-FD74-4810-950D-DD48290BA26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16590" yWindow="2325" windowWidth="18990" windowHeight="9255" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="2100" windowWidth="18990" windowHeight="9255" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="873">
   <si>
     <t>Fre</t>
   </si>
@@ -2707,6 +2707,22 @@
   </si>
   <si>
     <t>よぞら</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>变化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>へんげ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>体験</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たいけん</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -7537,7 +7553,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -9120,8 +9136,37 @@
         <v>0.75928861052748997</v>
       </c>
     </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105" s="2">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.75928861052748997</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A106" s="2">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0.75928861052748997</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LISTEN/Script/21_7/21_7.xlsx
+++ b/LISTEN/Script/21_7/21_7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\21_7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A57A748-FD74-4810-950D-DD48290BA26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A1D4A7-470E-4374-AB7C-D372638EFBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="2100" windowWidth="18990" windowHeight="9255" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="4275" windowWidth="23580" windowHeight="9255" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="873">
   <si>
     <t>Fre</t>
   </si>
@@ -7553,7 +7553,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -7563,7 +7563,7 @@
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7576,11 +7576,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -7593,11 +7590,8 @@
       <c r="D2" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="E2" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -7610,11 +7604,8 @@
       <c r="D3" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E3" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -7627,11 +7618,8 @@
       <c r="D4" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="E4" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -7641,11 +7629,8 @@
       <c r="C5" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="E5" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -7655,11 +7640,8 @@
       <c r="C6" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E6" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -7669,11 +7651,8 @@
       <c r="C7" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E7" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -7683,11 +7662,8 @@
       <c r="C8" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="E8" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -7700,11 +7676,8 @@
       <c r="D9" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="E9" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>2</v>
       </c>
@@ -7717,11 +7690,8 @@
       <c r="D10" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E10" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -7731,11 +7701,8 @@
       <c r="C11" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E11" s="2">
-        <v>0.37391203084270308</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -7745,11 +7712,8 @@
       <c r="C12" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E12" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>2</v>
       </c>
@@ -7759,11 +7723,8 @@
       <c r="C13" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="E13" s="2">
-        <v>0.39098940993909548</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -7776,11 +7737,8 @@
       <c r="D14" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E14" s="2">
-        <v>0.64039713127579212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -7793,11 +7751,8 @@
       <c r="D15" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="E15" s="2">
-        <v>0.45198331203026398</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>2</v>
       </c>
@@ -7810,11 +7765,8 @@
       <c r="D16" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="E16" s="2">
-        <v>0.83638686909894167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>1</v>
       </c>
@@ -7824,11 +7776,8 @@
       <c r="C17" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="E17" s="2">
-        <v>0.96238296292543946</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
         <v>2</v>
       </c>
@@ -7841,11 +7790,8 @@
       <c r="D18" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="E18" s="2">
-        <v>0.79014163472145893</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
         <v>2</v>
       </c>
@@ -7855,11 +7801,8 @@
       <c r="C19" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="E19" s="2">
-        <v>0.42109574185882659</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
         <v>2</v>
       </c>
@@ -7869,11 +7812,8 @@
       <c r="C20" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="E20" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
         <v>2</v>
       </c>
@@ -7883,11 +7823,8 @@
       <c r="C21" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="E21" s="2">
-        <v>0.62792138558333521</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
         <v>2</v>
       </c>
@@ -7897,11 +7834,8 @@
       <c r="C22" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="E22" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
         <v>2</v>
       </c>
@@ -7914,11 +7848,8 @@
       <c r="D23" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="E23" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
         <v>2</v>
       </c>
@@ -7928,11 +7859,8 @@
       <c r="C24" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="E24" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
         <v>1</v>
       </c>
@@ -7942,11 +7870,8 @@
       <c r="C25" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="E25" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
         <v>2</v>
       </c>
@@ -7959,11 +7884,8 @@
       <c r="D26" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="E26" s="2">
-        <v>0.87994695294981784</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
         <v>2</v>
       </c>
@@ -7973,11 +7895,8 @@
       <c r="C27" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="E27" s="2">
-        <v>0.54605638939527823</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
         <v>2</v>
       </c>
@@ -7987,11 +7906,8 @@
       <c r="C28" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="E28" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
         <v>1</v>
       </c>
@@ -8004,11 +7920,8 @@
       <c r="D29" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="E29" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
         <v>2</v>
       </c>
@@ -8021,11 +7934,8 @@
       <c r="D30" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="E30" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
         <v>1</v>
       </c>
@@ -8035,11 +7945,8 @@
       <c r="C31" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="E31" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
         <v>1</v>
       </c>
@@ -8049,11 +7956,8 @@
       <c r="C32" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="E32" s="2">
-        <v>0.60158237796834924</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
         <v>1</v>
       </c>
@@ -8066,11 +7970,8 @@
       <c r="D33" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="E33" s="2">
-        <v>0.22777657271152721</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
         <v>1</v>
       </c>
@@ -8083,11 +7984,8 @@
       <c r="D34" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="E34" s="2">
-        <v>0.73306874367158303</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
         <v>0</v>
       </c>
@@ -8097,11 +7995,8 @@
       <c r="C35" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="E35" s="2">
-        <v>0.86301015230476152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
         <v>0</v>
       </c>
@@ -8111,11 +8006,8 @@
       <c r="C36" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E36" s="2">
-        <v>0.67409344575197494</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="2">
         <v>1</v>
       </c>
@@ -8128,11 +8020,8 @@
       <c r="D37" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="E37" s="2">
-        <v>0.29168464700328878</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
         <v>0</v>
       </c>
@@ -8145,11 +8034,8 @@
       <c r="D38" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="E38" s="2">
-        <v>0.35596000880966128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
         <v>1</v>
       </c>
@@ -8162,11 +8048,8 @@
       <c r="D39" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="E39" s="2">
-        <v>0.86681970906242212</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="2">
         <v>1</v>
       </c>
@@ -8179,11 +8062,8 @@
       <c r="D40" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="E40" s="2">
-        <v>0.78364690909682855</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="2">
         <v>0</v>
       </c>
@@ -8196,11 +8076,8 @@
       <c r="D41" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="E41" s="2">
-        <v>0.2328990905000726</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="2">
         <v>0</v>
       </c>
@@ -8210,11 +8087,8 @@
       <c r="C42" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E42" s="2">
-        <v>0.75592014975790189</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="2">
         <v>1</v>
       </c>
@@ -8227,11 +8101,8 @@
       <c r="D43" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="E43" s="2">
-        <v>0.69587494766111679</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="2">
         <v>1</v>
       </c>
@@ -8244,11 +8115,8 @@
       <c r="D44" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="E44" s="2">
-        <v>0.71102623398289455</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="2">
         <v>1</v>
       </c>
@@ -8258,11 +8126,8 @@
       <c r="C45" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="E45" s="2">
-        <v>4.9026416878594103E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="2">
         <v>0</v>
       </c>
@@ -8275,11 +8140,8 @@
       <c r="D46" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="E46" s="2">
-        <v>0.18093973413670861</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="2">
         <v>0</v>
       </c>
@@ -8292,11 +8154,8 @@
       <c r="D47" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E47" s="2">
-        <v>0.66791242458487521</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="2">
         <v>1</v>
       </c>
@@ -8309,11 +8168,8 @@
       <c r="D48" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="E48" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="2">
         <v>0</v>
       </c>
@@ -8326,11 +8182,8 @@
       <c r="D49" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="E49" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -8340,11 +8193,8 @@
       <c r="C50" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="E50" s="2">
-        <v>0.52590814505581984</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="2">
         <v>1</v>
       </c>
@@ -8354,11 +8204,8 @@
       <c r="C51" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="E51" s="2">
-        <v>0.52540287528012997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
         <v>0</v>
       </c>
@@ -8371,11 +8218,8 @@
       <c r="D52" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="E52" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
         <v>1</v>
       </c>
@@ -8388,11 +8232,8 @@
       <c r="D53" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="E53" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="2">
         <v>0</v>
       </c>
@@ -8405,11 +8246,8 @@
       <c r="D54" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="E54" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="2">
         <v>0</v>
       </c>
@@ -8419,11 +8257,8 @@
       <c r="C55" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="E55" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="2">
         <v>1</v>
       </c>
@@ -8436,11 +8271,8 @@
       <c r="D56" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="E56" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="2">
         <v>0</v>
       </c>
@@ -8453,11 +8285,8 @@
       <c r="D57" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="E57" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="2">
         <v>1</v>
       </c>
@@ -8467,11 +8296,8 @@
       <c r="C58" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="E58" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="2">
         <v>0</v>
       </c>
@@ -8481,11 +8307,8 @@
       <c r="C59" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="E59" s="2">
-        <v>0.95556960903751897</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="2">
         <v>0</v>
       </c>
@@ -8498,11 +8321,8 @@
       <c r="D60" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="E60" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="2">
         <v>0</v>
       </c>
@@ -8512,11 +8332,8 @@
       <c r="C61" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="E61" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="2">
         <v>1</v>
       </c>
@@ -8526,11 +8343,8 @@
       <c r="C62" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="E62" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="2">
         <v>1</v>
       </c>
@@ -8543,11 +8357,8 @@
       <c r="D63" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="E63" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="2">
         <v>0</v>
       </c>
@@ -8557,11 +8368,8 @@
       <c r="C64" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="E64" s="2">
-        <v>0.78634294646323966</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="2">
         <v>1</v>
       </c>
@@ -8574,11 +8382,8 @@
       <c r="D65" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="E65" s="2">
-        <v>0.42263283947775993</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="2">
         <v>0</v>
       </c>
@@ -8588,11 +8393,8 @@
       <c r="C66" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="E66" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="2">
         <v>1</v>
       </c>
@@ -8602,11 +8404,8 @@
       <c r="C67" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="E67" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="2">
         <v>0</v>
       </c>
@@ -8616,11 +8415,8 @@
       <c r="C68" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="E68" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
         <v>0</v>
       </c>
@@ -8630,11 +8426,8 @@
       <c r="C69" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="E69" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
         <v>0</v>
       </c>
@@ -8644,11 +8437,8 @@
       <c r="C70" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="E70" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="2">
         <v>0</v>
       </c>
@@ -8658,11 +8448,8 @@
       <c r="C71" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="E71" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="2">
         <v>0</v>
       </c>
@@ -8672,11 +8459,8 @@
       <c r="C72" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="E72" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="2">
         <v>0</v>
       </c>
@@ -8686,11 +8470,8 @@
       <c r="C73" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="E73" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="2">
         <v>0</v>
       </c>
@@ -8700,11 +8481,8 @@
       <c r="C74" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="E74" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="2">
         <v>0</v>
       </c>
@@ -8714,11 +8492,8 @@
       <c r="C75" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="E75" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="2">
         <v>0</v>
       </c>
@@ -8728,11 +8503,8 @@
       <c r="C76" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="E76" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="2">
         <v>0</v>
       </c>
@@ -8742,11 +8514,8 @@
       <c r="C77" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="E77" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="2">
         <v>0</v>
       </c>
@@ -8756,11 +8525,8 @@
       <c r="C78" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="E78" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="2">
         <v>0</v>
       </c>
@@ -8770,11 +8536,8 @@
       <c r="C79" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="E79" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="2">
         <v>0</v>
       </c>
@@ -8784,11 +8547,8 @@
       <c r="C80" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="E80" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
         <v>0</v>
       </c>
@@ -8801,11 +8561,8 @@
       <c r="D81" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="E81" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="2">
         <v>0</v>
       </c>
@@ -8815,11 +8572,8 @@
       <c r="C82" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="E82" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="2">
         <v>0</v>
       </c>
@@ -8829,11 +8583,8 @@
       <c r="C83" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="E83" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="2">
         <v>0</v>
       </c>
@@ -8843,11 +8594,8 @@
       <c r="C84" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="E84" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="2">
         <v>0</v>
       </c>
@@ -8857,11 +8605,8 @@
       <c r="C85" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="E85" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="2">
         <v>0</v>
       </c>
@@ -8871,11 +8616,8 @@
       <c r="C86" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="E86" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="2">
         <v>0</v>
       </c>
@@ -8885,11 +8627,8 @@
       <c r="C87" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="E87" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="2">
         <v>0</v>
       </c>
@@ -8902,11 +8641,8 @@
       <c r="D88" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="E88" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="2">
         <v>0</v>
       </c>
@@ -8916,11 +8652,8 @@
       <c r="C89" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="E89" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="2">
         <v>0</v>
       </c>
@@ -8930,11 +8663,8 @@
       <c r="C90" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="E90" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="2">
         <v>0</v>
       </c>
@@ -8944,11 +8674,8 @@
       <c r="C91" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="E91" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="2">
         <v>0</v>
       </c>
@@ -8958,11 +8685,8 @@
       <c r="C92" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="E92" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="2">
         <v>0</v>
       </c>
@@ -8972,11 +8696,8 @@
       <c r="C93" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="E93" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="2">
         <v>0</v>
       </c>
@@ -8986,11 +8707,8 @@
       <c r="C94" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="E94" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="2">
         <v>0</v>
       </c>
@@ -9000,11 +8718,8 @@
       <c r="C95" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E95" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="2">
         <v>0</v>
       </c>
@@ -9014,11 +8729,8 @@
       <c r="C96" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="E96" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="2">
         <v>0</v>
       </c>
@@ -9028,11 +8740,8 @@
       <c r="C97" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="E97" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="2">
         <v>0</v>
       </c>
@@ -9042,11 +8751,8 @@
       <c r="C98" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="E98" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="2">
         <v>0</v>
       </c>
@@ -9059,11 +8765,8 @@
       <c r="D99" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E99" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="2">
         <v>0</v>
       </c>
@@ -9073,11 +8776,8 @@
       <c r="C100" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="E100" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="2">
         <v>0</v>
       </c>
@@ -9087,11 +8787,8 @@
       <c r="C101" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="E101" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="2">
         <v>0</v>
       </c>
@@ -9101,11 +8798,8 @@
       <c r="C102" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="E102" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="2">
         <v>0</v>
       </c>
@@ -9118,11 +8812,8 @@
       <c r="D103" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="E103" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="2">
         <v>0</v>
       </c>
@@ -9132,11 +8823,8 @@
       <c r="C104" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="E104" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="2">
         <v>0</v>
       </c>
@@ -9146,11 +8834,8 @@
       <c r="C105" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="E105" s="2">
-        <v>0.75928861052748997</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="2">
         <v>0</v>
       </c>
@@ -9159,9 +8844,6 @@
       </c>
       <c r="C106" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="E106" s="2">
-        <v>0.75928861052748997</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/21_7/21_7.xlsx
+++ b/LISTEN/Script/21_7/21_7.xlsx
@@ -1972,7 +1972,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1991,21 +1991,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>適切</t>
+          <t>居間</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>てきせつ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>客厅</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>0.01419579634335133</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="4">
@@ -2014,17 +2018,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>解説</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>かいせつ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>めんきょ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>许可证；执照</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>0.3974750454523346</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="5">
@@ -2033,12 +2037,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>文法</t>
+          <t>海上</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ぶんぽう</t>
+          <t>かいじょう</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2052,17 +2056,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>住む</t>
+          <t>盛</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>すむ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>さかん</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>兴盛；繁荣；旺盛</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.7019839433581557</v>
       </c>
     </row>
     <row r="7">
@@ -2071,17 +2079,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>昨夜</t>
+          <t>勝る</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>さくや</t>
+          <t>まさる</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.9902902942540005</v>
       </c>
     </row>
     <row r="8">
@@ -2090,21 +2098,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>学ぶ</t>
+          <t>上回る</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>まなぶ</t>
+          <t>うわまわる</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>学习；模仿</t>
+          <t>超过；胜过</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.6761341142362004</v>
       </c>
     </row>
     <row r="9">
@@ -2113,21 +2121,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>送る</t>
+          <t>昨夜</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>おくる</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>寄送；传递</t>
-        </is>
-      </c>
+          <t>さくや</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.3425329101118375</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="10">
@@ -2136,21 +2140,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>上回る</t>
+          <t>学ぶ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>うわまわる</t>
+          <t>まなぶ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>超过；胜过</t>
+          <t>学习；模仿</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6761341142362004</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="11">
@@ -2159,21 +2163,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>手当</t>
+          <t>解説</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>てあて</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>补贴；津贴；治疗</t>
-        </is>
-      </c>
+          <t>かいせつ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.3974750454523346</v>
       </c>
     </row>
     <row r="12">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>勝る</t>
+          <t>住む</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>まさる</t>
+          <t>すむ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.9902902942540005</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="13">
@@ -2201,21 +2201,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>盛</t>
+          <t>文法</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>さかん</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>兴盛；繁荣；旺盛</t>
-        </is>
-      </c>
+          <t>ぶんぽう</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.7019839433581557</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="14">
@@ -2224,12 +2220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>海上</t>
+          <t>燃</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>かいじょう</t>
+          <t>もえ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2243,17 +2239,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>燃</t>
+          <t>送る</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>もえ</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>おくる</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>寄送；传递</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.3425329101118375</v>
       </c>
     </row>
     <row r="16">
@@ -2262,13 +2262,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>めんきょ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>手当</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>てあて</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>许可证；执照</t>
+          <t>补贴；津贴；治疗</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2281,19 +2285,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>居間</t>
+          <t>自宅</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>いま</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>客厅</t>
-        </is>
-      </c>
+          <t>じたく</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2304,17 +2304,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ぎじゅつてき</t>
+          <t>応募</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>技術的</t>
+          <t>おうぼ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.4159316045857645</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="19">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>ぎじゅつてき</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>きぼう</t>
+          <t>技術的</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.4159316045857645</v>
       </c>
     </row>
     <row r="20">
@@ -2342,15 +2342,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>トラック</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>卡车；货车</t>
-        </is>
-      </c>
+          <t>表現</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ひょうげん</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2361,17 +2361,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>かんとく</t>
+          <t>現場</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>監督</t>
+          <t>げんば</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.7901882351065465</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="22">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>低気圧</t>
+          <t>適切</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ていきあつ</t>
+          <t>てきせつ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.01419579634335133</v>
       </c>
     </row>
     <row r="23">
@@ -2399,15 +2399,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>乗用車</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>じょうようしゃ</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>ひどい</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>严重的；过分的</t>
+        </is>
+      </c>
       <c r="E23" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>応募</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>おうぼ</t>
+          <t>ないよう</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2437,15 +2437,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ひどい</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>严重的；过分的</t>
-        </is>
-      </c>
+          <t>乗用車</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>じょうようしゃ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>自宅</t>
+          <t>低気圧</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>じたく</t>
+          <t>ていきあつ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2475,17 +2475,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>かんとく</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ないよう</t>
+          <t>監督</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.7901882351065465</v>
       </c>
     </row>
     <row r="28">
@@ -2494,15 +2494,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>現場</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>げんば</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>トラック</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>卡车；货车</t>
+        </is>
+      </c>
       <c r="E28" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>表現</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ひょうげん</t>
+          <t>きぼう</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2532,17 +2532,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ばしょ</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>グリーン</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.1714034957194206</v>
       </c>
     </row>
     <row r="31">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>勝敗</t>
+          <t>場所</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>しょうはい</t>
+          <t>ばしょ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>実は</t>
+          <t>勝敗</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>じつは</t>
+          <t>しょうはい</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2589,17 +2589,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>グリーン</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
+          <t>実は</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>じつは</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>0.1714034957194206</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="34">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>免許</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ひ</t>
+          <t>めんきょ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>免許</t>
+          <t>指定</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>めんきょ</t>
+          <t>してい</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.5200831809049434</v>
       </c>
     </row>
     <row r="42">
@@ -2768,17 +2768,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>指定</t>
+          <t>終了</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>してい</t>
+          <t>しゅうりょう</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>0.5200831809049434</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="43">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>終了</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>しゅうりょう</t>
+          <t>ひ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2806,17 +2806,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>募集</t>
+          <t>蒸し暑い</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ぼしゅう</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>むしあつい</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>闷热；潮湿炎热</t>
+        </is>
+      </c>
       <c r="E44" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.9348661848164155</v>
       </c>
     </row>
     <row r="45">
@@ -2825,19 +2829,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>割れる</t>
+          <t>募集</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>われる</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>裂开；分裂</t>
-        </is>
-      </c>
+          <t>ぼしゅう</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2848,15 +2848,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>雲</t>
+          <t>割れる</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>くも</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>われる</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>裂开；分裂</t>
+        </is>
+      </c>
       <c r="E46" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2867,19 +2871,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>レジ</t>
+          <t>雲</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>レジ</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>收银</t>
-        </is>
-      </c>
+          <t>くも</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -2890,21 +2890,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>蒸し暑い</t>
+          <t>大雨</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>むしあつい</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>闷热；潮湿炎热</t>
-        </is>
-      </c>
+          <t>おおあめ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>0.9348661848164155</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="49">
@@ -2936,17 +2932,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>多い</t>
+          <t>レジ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>おおい</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>レジ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>收银</t>
+        </is>
+      </c>
       <c r="E50" t="n">
-        <v>0.7269855550698141</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="51">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>大雨</t>
+          <t>参加者</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>おおあめ</t>
+          <t>さんかしゃ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2997,15 +2997,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>参加者</t>
+          <t>台所</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>さんかしゃ</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>だいどころ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>厨房；灶间</t>
+        </is>
+      </c>
       <c r="E53" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -3016,21 +3020,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>台所</t>
+          <t>仕方</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>だいどころ</t>
+          <t>しかた</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>厨房；灶间</t>
+          <t>方法；办法</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.5323788339693154</v>
       </c>
     </row>
     <row r="55">
@@ -3039,21 +3043,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>仕方</t>
+          <t>影響</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>しかた</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>方法；办法</t>
-        </is>
-      </c>
+          <t>えいきょう</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>0.5323788339693154</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="56">
@@ -3062,17 +3062,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>多い</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>えいきょう</t>
+          <t>おおい</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.7269855550698141</v>
       </c>
     </row>
     <row r="57">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>覧</t>
+          <t>勝つ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>らん</t>
+          <t>かつ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>0.3509684665628668</v>
+        <v>0.1527449435361916</v>
       </c>
     </row>
     <row r="58">
@@ -3100,21 +3100,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>都合</t>
+          <t>覧</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>つごう</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>情况；方便；安排</t>
-        </is>
-      </c>
+          <t>らん</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.3509684665628668</v>
       </c>
     </row>
     <row r="59">
@@ -3123,21 +3119,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>大事</t>
+          <t>都合</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>だいじ</t>
+          <t>つごう</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>重要；重大</t>
+          <t>情况；方便；安排</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.4959383850123251</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="60">
@@ -3146,21 +3142,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>話せる</t>
+          <t>大事</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>はなせる</t>
+          <t>だいじ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>能说，会说</t>
+          <t>重要；重大</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.4959383850123251</v>
       </c>
     </row>
     <row r="61">
@@ -3169,15 +3165,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>例え</t>
+          <t>話せる</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>たとえ</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>はなせる</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>能说，会说</t>
+        </is>
+      </c>
       <c r="E61" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -3188,19 +3188,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>教え方</t>
+          <t>例え</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>おしえかた</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>教学方法</t>
-        </is>
-      </c>
+          <t>たとえ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -3211,17 +3207,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>言葉</t>
+          <t>教え方</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ことば</t>
+          <t>おしえかた</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>语言；言辞</t>
+          <t>教学方法</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -3234,15 +3230,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>計画</t>
+          <t>言葉</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>けいかく</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>ことば</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>语言；言辞</t>
+        </is>
+      </c>
       <c r="E64" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -3253,21 +3253,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>落ちる</t>
+          <t>計画</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>おちる</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>落下；坠落；跌落</t>
-        </is>
-      </c>
+          <t>けいかく</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>0.4519443540378616</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="66">
@@ -3276,17 +3272,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>意外</t>
+          <t>落ちる</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>いがい</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>おちる</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>落下；坠落；跌落</t>
+        </is>
+      </c>
       <c r="E66" t="n">
-        <v>0.5737801670611312</v>
+        <v>0.4519443540378616</v>
       </c>
     </row>
     <row r="67">
@@ -3295,17 +3295,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>勝つ</t>
+          <t>監督</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>かつ</t>
+          <t>かんとく</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>0.1527449435361916</v>
+        <v>0.7116210179740582</v>
       </c>
     </row>
     <row r="68">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>監督</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>かんとく</t>
+          <t>じしん</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>0.7116210179740582</v>
+        <v>0.05900641249864114</v>
       </c>
     </row>
     <row r="69">
@@ -3333,21 +3333,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>試合</t>
+          <t>軽い</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>しあい</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>比赛; 竞赛</t>
-        </is>
-      </c>
+          <t>かるい</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>0.4705335632651936</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="70">
@@ -3356,17 +3352,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>運動量</t>
+          <t>試合</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>うんどうりょう</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>しあい</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>比赛; 竞赛</t>
+        </is>
+      </c>
       <c r="E70" t="n">
-        <v>0.2691084671400232</v>
+        <v>0.4705335632651936</v>
       </c>
     </row>
     <row r="71">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>最高</t>
+          <t>運動量</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>さいこう</t>
+          <t>うんどうりょう</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.6615553225464611</v>
+        <v>0.2691084671400232</v>
       </c>
     </row>
     <row r="72">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>べんち</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>长凳;替补席</t>
-        </is>
-      </c>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>さいこう</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>0.8398577739942041</v>
+        <v>0.6615553225464611</v>
       </c>
     </row>
     <row r="73">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>最後</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>さいご</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>べんち</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>长凳;替补席</t>
+        </is>
+      </c>
       <c r="E73" t="n">
-        <v>0.392555804278785</v>
+        <v>0.8398577739942041</v>
       </c>
     </row>
     <row r="74">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>主に</t>
+          <t>最後</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>おもに</t>
+          <t>さいご</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.392555804278785</v>
       </c>
     </row>
     <row r="75">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>主に</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>げんいん</t>
+          <t>おもに</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>地域</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ちいき</t>
+          <t>げんいん</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -3489,19 +3489,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>勤務日</t>
+          <t>地域</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>きんむび</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>工作日；上班日</t>
-        </is>
-      </c>
+          <t>ちいき</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -3512,17 +3508,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>自身</t>
+          <t>意外</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>じしん</t>
+          <t>いがい</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>0.05900641249864114</v>
+        <v>0.5737801670611312</v>
       </c>
     </row>
     <row r="79">
@@ -3531,12 +3527,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>軽い</t>
+          <t>配達</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>かるい</t>
+          <t>はいたつ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3550,15 +3546,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>逃げる</t>
+          <t>勤務日</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>にげる</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>きんむび</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>工作日；上班日</t>
+        </is>
+      </c>
       <c r="E80" t="n">
         <v>0.7933423773713529</v>
       </c>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>郵便局</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ゆうびんきょく</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>チラシ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>传单</t>
+        </is>
+      </c>
       <c r="E81" t="n">
-        <v>0.3323464141988581</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="82">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>今回</t>
+          <t>選手</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>こんかい</t>
+          <t>せんしゅ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.1524787084139845</v>
       </c>
     </row>
     <row r="83">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>指示</t>
+          <t>今回</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>しじ</t>
+          <t>こんかい</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.1648760954996494</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="84">
@@ -3626,21 +3626,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>夕方</t>
+          <t>指示</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ゆうがた</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>傍晚；黄昏</t>
-        </is>
-      </c>
+          <t>しじ</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.1648760954996494</v>
       </c>
     </row>
     <row r="85">
@@ -3649,21 +3645,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>荷物</t>
+          <t>夕方</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>にもつ</t>
+          <t>ゆうがた</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>行李;货物</t>
+          <t>傍晚；黄昏</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.2736042843241824</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="86">
@@ -3672,17 +3668,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>火事</t>
+          <t>荷物</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>かじ</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>にもつ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>行李;货物</t>
+        </is>
+      </c>
       <c r="E86" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.2736042843241824</v>
       </c>
     </row>
     <row r="87">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>爽やか</t>
+          <t>火事</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>さわやか</t>
+          <t>かじ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>遠い</t>
+          <t>爽やか</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>とおい</t>
+          <t>さわやか</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>理由</t>
+          <t>遠い</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>りゆう</t>
+          <t>とおい</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>0.2532109880689026</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="90">
@@ -3748,17 +3748,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>チラシ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>传单</t>
-        </is>
-      </c>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>りゆう</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.2532109880689026</v>
       </c>
     </row>
     <row r="91">
@@ -3767,17 +3767,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>選手</t>
+          <t>二階</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>せんしゅ</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>にかい</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>二楼</t>
+        </is>
+      </c>
       <c r="E91" t="n">
-        <v>0.1524787084139845</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="92">
@@ -3786,17 +3790,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>留守</t>
+          <t>郵便局</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>るす</t>
+          <t>ゆうびんきょく</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>0.5367602745752723</v>
+        <v>0.3323464141988581</v>
       </c>
     </row>
     <row r="93">
@@ -3805,21 +3809,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>二階</t>
+          <t>留守</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>にかい</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>二楼</t>
-        </is>
-      </c>
+          <t>るす</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.5367602745752723</v>
       </c>
     </row>
     <row r="94">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>体力</t>
+          <t>逃げる</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>たいりょく</t>
+          <t>にげる</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>0.0947149919380269</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="95">
@@ -3847,17 +3847,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>体力</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ちょうさ</t>
+          <t>たいりょく</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.0947149919380269</v>
       </c>
     </row>
     <row r="96">
@@ -3866,21 +3866,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>優れる</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>すぐれる</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>优秀；出色</t>
-        </is>
-      </c>
+          <t>ちょうさ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>0.9964383118488522</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="97">
@@ -3889,17 +3885,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>採用</t>
+          <t>優れる</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>さいよう</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>すぐれる</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>优秀；出色</t>
+        </is>
+      </c>
       <c r="E97" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.9964383118488522</v>
       </c>
     </row>
     <row r="98">
@@ -3908,21 +3908,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>無理</t>
+          <t>採用</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>むり</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>不可能；勉强</t>
-        </is>
-      </c>
+          <t>さいよう</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0.09428482783138015</v>
+        <v>0.7933423773713529</v>
       </c>
     </row>
     <row r="99">
@@ -3931,21 +3927,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>届く</t>
+          <t>無理</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>とどく</t>
+          <t>むり</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>送达；收到</t>
+          <t>不可能；勉强</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.2703117313850503</v>
+        <v>0.09428482783138015</v>
       </c>
     </row>
     <row r="100">
@@ -3954,17 +3950,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>市内</t>
+          <t>届く</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>しない</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>とどく</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>送达；收到</t>
+        </is>
+      </c>
       <c r="E100" t="n">
-        <v>0.7933423773713529</v>
+        <v>0.2703117313850503</v>
       </c>
     </row>
     <row r="101">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>配達</t>
+          <t>市内</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>はいたつ</t>
+          <t>しない</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -4071,158 +4071,162 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>自治体</t>
+          <t>存分</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>じちたい</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ぞんぶん</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>尽情；充分</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>0.9676069026731489</v>
+        <v>0.05844095587181231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>増やす</t>
+          <t>代表的な</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ふやす</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>增加；增多</t>
-        </is>
-      </c>
+          <t>だいひょうてきな</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.1724141758911374</v>
+        <v>0.2009770378804967</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>決心</t>
+          <t>つられる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>けっしん</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>つられる</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>被吸引，つる的被动</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>0.3111695784487023</v>
+        <v>0.8301614267053162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>対応</t>
+          <t>陸上競技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>たいおう</t>
+          <t>りくじょうきょうぎ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.2857484059511959</v>
+        <v>0.01357451936647236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>感謝</t>
+          <t>ふわふわ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>かんしゃ</t>
+          <t>轻盈、蓬松、漂浮</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.1678489571729138</v>
+        <v>0.07444685867237044</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>開催</t>
+          <t>植物</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>かいさい</t>
+          <t>しょくぶつ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>0.05331196481348999</v>
+        <v>0.5626733302674656</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>飛ぶ</t>
+          <t>環境</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>とぶ</t>
+          <t>かんきょう</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.4265832880224659</v>
+        <v>0.9482497886368535</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>飼う</t>
+          <t>調査</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>かう</t>
+          <t>ちょうさ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>0.7637207215328199</v>
+        <v>0.08246408338231415</v>
       </c>
     </row>
     <row r="11">
@@ -4231,18 +4235,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>招く</t>
+          <t>張り切る</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>まねく</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.6337847961512131</v>
-      </c>
+          <t>はりきる</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>干劲十足</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4250,17 +4256,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>減る</t>
+          <t>対応</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>へる</t>
+          <t>たいおう</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.5207735291644779</v>
+        <v>0.2857484059511959</v>
       </c>
     </row>
     <row r="13">
@@ -4269,17 +4275,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>考う</t>
+          <t>感謝</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>かんがう</t>
+          <t>かんしゃ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.4326251809062334</v>
+        <v>0.1678489571729138</v>
       </c>
     </row>
     <row r="14">
@@ -4288,20 +4294,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>張り切る</t>
+          <t>開催</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>はりきる</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>干劲十足</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>かいさい</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0.05331196481348999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4309,17 +4313,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>経済</t>
+          <t>飛ぶ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>けいざい</t>
+          <t>とぶ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.7241599553239286</v>
+        <v>0.4265832880224659</v>
       </c>
     </row>
     <row r="16">
@@ -4328,17 +4332,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>事情</t>
+          <t>飼う</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>じじょう</t>
+          <t>かう</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>0.6709968823344724</v>
+        <v>0.7637207215328199</v>
       </c>
     </row>
     <row r="17">
@@ -4347,21 +4351,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>共働き</t>
+          <t>減る</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ともばたらき</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>双职工；夫妻都工作</t>
-        </is>
-      </c>
+          <t>へる</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>0.9827837585755766</v>
+        <v>0.5207735291644779</v>
       </c>
     </row>
     <row r="18">
@@ -4370,21 +4370,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>連る</t>
+          <t>招く</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>つる</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>牵连；牵涉；连累</t>
-        </is>
-      </c>
+          <t>まねく</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.4122314519957648</v>
+        <v>0.6337847961512131</v>
       </c>
     </row>
     <row r="19">
@@ -4393,17 +4389,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>早期</t>
+          <t>連る</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>そうき</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>つる</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>牵连；牵涉；连累</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>0.5961765777184475</v>
+        <v>0.4122314519957648</v>
       </c>
     </row>
     <row r="20">
@@ -4412,21 +4412,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>飼い</t>
+          <t>経済</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>かい</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>饲养；喂养</t>
-        </is>
-      </c>
+          <t>けいざい</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.4403997994848168</v>
+        <v>0.7241599553239286</v>
       </c>
     </row>
     <row r="21">
@@ -4435,21 +4431,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>宿泊</t>
+          <t>事情</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>しゅくはく</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>住宿</t>
-        </is>
-      </c>
+          <t>じじょう</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.06760923933021235</v>
+        <v>0.6709968823344724</v>
       </c>
     </row>
     <row r="22">
@@ -4458,17 +4450,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>風</t>
+          <t>共働き</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>かぜ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>ともばたらき</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>双职工；夫妻都工作</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>0.8013836844529532</v>
+        <v>0.9827837585755766</v>
       </c>
     </row>
     <row r="23">
@@ -4477,17 +4473,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>理解</t>
+          <t>決心</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>りかい</t>
+          <t>けっしん</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>0.6787443174761142</v>
+        <v>0.3111695784487023</v>
       </c>
     </row>
     <row r="24">
@@ -4496,17 +4492,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>全国</t>
+          <t>早期</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ぜんこく</t>
+          <t>そうき</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>0.2704837178757165</v>
+        <v>0.5961765777184475</v>
       </c>
     </row>
     <row r="25">
@@ -4515,17 +4511,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>飼い</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ほうほう</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>かい</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>饲养；喂养</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>0.5472933787585305</v>
+        <v>0.4403997994848168</v>
       </c>
     </row>
     <row r="26">
@@ -4534,21 +4534,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>建て替える</t>
+          <t>風</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>たてかえる</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>重建；改建</t>
-        </is>
-      </c>
+          <t>かぜ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.8490505489274927</v>
+        <v>0.8013836844529532</v>
       </c>
     </row>
     <row r="27">
@@ -4557,17 +4553,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>調査</t>
+          <t>増やす</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ちょうさ</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>ふやす</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>增加；增多</t>
+        </is>
+      </c>
       <c r="E27" t="n">
-        <v>0.08246408338231415</v>
+        <v>0.1724141758911374</v>
       </c>
     </row>
     <row r="28">
@@ -4576,17 +4576,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>宿泊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>かんきょう</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>しゅくはく</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
       <c r="E28" t="n">
-        <v>0.9482497886368535</v>
+        <v>0.06760923933021235</v>
       </c>
     </row>
     <row r="29">
@@ -4595,17 +4599,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>植物</t>
+          <t>理解</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>しょくぶつ</t>
+          <t>りかい</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>0.5626733302674656</v>
+        <v>0.6787443174761142</v>
       </c>
     </row>
     <row r="30">
@@ -4614,21 +4618,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>存分</t>
+          <t>協力</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ぞんぶん</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>尽情；充分</t>
-        </is>
-      </c>
+          <t>きょうりょく</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.05844095587181231</v>
+        <v>0.2438903514514572</v>
       </c>
     </row>
     <row r="31">
@@ -4637,17 +4637,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>陸上競技</t>
+          <t>考う</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>りくじょうきょうぎ</t>
+          <t>かんがう</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>0.01357451936647236</v>
+        <v>0.4326251809062334</v>
       </c>
     </row>
     <row r="32">
@@ -4656,21 +4656,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>つられる</t>
+          <t>真っ白</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>つられる</t>
+          <t>まっしろ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>被吸引，つる的被动</t>
+          <t>纯白；洁白</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.8301614267053162</v>
+        <v>0.9922224864131055</v>
       </c>
     </row>
     <row r="33">
@@ -4679,17 +4679,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ふわふわ</t>
+          <t>成分</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>轻盈、蓬松、漂浮</t>
+          <t>せいぶん</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>0.07444685867237044</v>
+        <v>0.5308511849032185</v>
       </c>
     </row>
     <row r="34">
@@ -4698,17 +4698,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>成分</t>
+          <t>気付</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>せいぶん</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>きづけ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>注意；察觉；意识；关心</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>0.5308511849032185</v>
+        <v>0.2553595371950442</v>
       </c>
     </row>
     <row r="35">
@@ -4717,21 +4721,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>真っ白</t>
+          <t>方法</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>まっしろ</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>纯白；洁白</t>
-        </is>
-      </c>
+          <t>ほうほう</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.9922224864131055</v>
+        <v>0.5472933787585305</v>
       </c>
     </row>
     <row r="36">
@@ -4740,17 +4740,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>代表的な</t>
+          <t>塊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>だいひょうてきな</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>かたまり</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>块；团；堆</t>
+        </is>
+      </c>
       <c r="E36" t="n">
-        <v>0.2009770378804967</v>
+        <v>0.8416161725406397</v>
       </c>
     </row>
     <row r="37">
@@ -4759,21 +4763,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>気付</t>
+          <t>整備</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>きづけ</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>注意；察觉；意识；关心</t>
-        </is>
-      </c>
+          <t>せいび</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>0.2553595371950442</v>
+        <v>0.533551365388601</v>
       </c>
     </row>
     <row r="38">
@@ -4782,21 +4782,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>塊</t>
+          <t>議会</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>かたまり</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>块；团；堆</t>
-        </is>
-      </c>
+          <t>ぎかい</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>0.8416161725406397</v>
+        <v>0.0983013494872903</v>
       </c>
     </row>
     <row r="39">
@@ -4805,17 +4801,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>整備</t>
+          <t>生活</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>せいび</t>
+          <t>せいかつ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.533551365388601</v>
+        <v>0.9439796845037546</v>
       </c>
     </row>
     <row r="40">
@@ -4824,17 +4820,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>議会</t>
+          <t>発見</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ぎかい</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>はっけん</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>发现；发觉</t>
+        </is>
+      </c>
       <c r="E40" t="n">
-        <v>0.0983013494872903</v>
+        <v>0.8150258871480548</v>
       </c>
     </row>
     <row r="41">
@@ -4843,17 +4843,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>協力</t>
+          <t>工夫</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>きょうりょく</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>こうふ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>想办法；动脑筋；设法</t>
+        </is>
+      </c>
       <c r="E41" t="n">
-        <v>0.2438903514514572</v>
+        <v>0.3668959478990358</v>
       </c>
     </row>
     <row r="42">
@@ -4862,17 +4866,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>生活</t>
+          <t>道路</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>せいかつ</t>
+          <t>どうろ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>0.9439796845037546</v>
+        <v>0.2306078103797546</v>
       </c>
     </row>
     <row r="43">
@@ -4881,21 +4885,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>発見</t>
+          <t>自治体</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>はっけん</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>发现；发觉</t>
-        </is>
-      </c>
+          <t>じちたい</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>0.8150258871480548</v>
+        <v>0.9676069026731489</v>
       </c>
     </row>
     <row r="44">
@@ -4904,21 +4904,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>工夫</t>
+          <t>建て替える</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>こうふ</t>
+          <t>たてかえる</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>想办法；动脑筋；设法</t>
+          <t>重建；改建</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3668959478990358</v>
+        <v>0.8490505489274927</v>
       </c>
     </row>
     <row r="45">
@@ -4946,17 +4946,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>道路</t>
+          <t>全国</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>どうろ</t>
+          <t>ぜんこく</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>0.2306078103797546</v>
+        <v>0.2704837178757165</v>
       </c>
     </row>
     <row r="47">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>山川市</t>
+          <t>変化</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>やまかわし</t>
+          <t>へんか</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>0.1145043861620015</v>
+        <v>0.6686736362670953</v>
       </c>
     </row>
     <row r="48">
@@ -4984,21 +4984,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>番組</t>
+          <t>山川市</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ばんぐみ</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>节目</t>
-        </is>
-      </c>
+          <t>やまかわし</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>0.5284131913765537</v>
+        <v>0.1145043861620015</v>
       </c>
     </row>
     <row r="49">
@@ -5007,17 +5003,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>急ぐ</t>
+          <t>番組</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>いそぐ</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>ばんぐみ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>节目</t>
+        </is>
+      </c>
       <c r="E49" t="n">
-        <v>0.5284680002490183</v>
+        <v>0.5284131913765537</v>
       </c>
     </row>
     <row r="50">
@@ -5026,17 +5026,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>急ぐ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>かてい</t>
+          <t>いそぐ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>0.3520377056456966</v>
+        <v>0.5284680002490183</v>
       </c>
     </row>
     <row r="51">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>医療費</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>いりょうひ</t>
+          <t>かてい</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>0.20982623469991</v>
+        <v>0.3520377056456966</v>
       </c>
     </row>
     <row r="52">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>変化</t>
+          <t>医療費</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>へんか</t>
+          <t>いりょうひ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>0.6686736362670953</v>
+        <v>0.20982623469991</v>
       </c>
     </row>
     <row r="53">
@@ -5083,17 +5083,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>洗濯</t>
+          <t>残る</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>せんたく</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>のこる</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>剩余；遗留</t>
+        </is>
+      </c>
       <c r="E53" t="n">
-        <v>0.6113957108835867</v>
+        <v>0.8070474705457454</v>
       </c>
     </row>
     <row r="54">
@@ -5102,17 +5106,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>釣り</t>
+          <t>蟻</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>つり</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>蚂蚁</t>
+        </is>
+      </c>
       <c r="E54" t="n">
-        <v>0.1566313768025568</v>
+        <v>0.1302451386153273</v>
       </c>
     </row>
     <row r="55">
@@ -5121,21 +5129,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>蟻</t>
+          <t>体</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>あり</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>蚂蚁</t>
-        </is>
-      </c>
+          <t>からだ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>0.1302451386153273</v>
+        <v>0.8155391661982546</v>
       </c>
     </row>
     <row r="56">
@@ -5144,17 +5148,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>体</t>
+          <t>やりがい</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>からだ</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>やりがい</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>有价值</t>
+        </is>
+      </c>
       <c r="E56" t="n">
-        <v>0.8155391661982546</v>
+        <v>0.8941242932561488</v>
       </c>
     </row>
     <row r="57">
@@ -5163,21 +5171,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>残る</t>
+          <t>洗濯</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>のこる</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>剩余；遗留</t>
-        </is>
-      </c>
+          <t>せんたく</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>0.8070474705457454</v>
+        <v>0.6113957108835867</v>
       </c>
     </row>
     <row r="58">
@@ -5186,21 +5190,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>やりがい</t>
+          <t>釣り</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>やりがい</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>有价值</t>
-        </is>
-      </c>
+          <t>つり</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>0.8941242932561488</v>
+        <v>0.1566313768025568</v>
       </c>
     </row>
     <row r="59">
@@ -5209,17 +5209,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>歩く</t>
+          <t>つく</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>あるく</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>つく</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>附着</t>
+        </is>
+      </c>
       <c r="E59" t="n">
-        <v>0.3094299906015364</v>
+        <v>0.4699041995021516</v>
       </c>
     </row>
     <row r="60">
@@ -5228,21 +5232,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>仲間</t>
+          <t>確保</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>なかま</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>同伴；伙伴</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> かくほ</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>0.5916809050701822</v>
+        <v>0.5869566020980956</v>
       </c>
     </row>
     <row r="61">
@@ -5251,21 +5251,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>〜向けの</t>
+          <t>乗る</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>むけの</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>面向…</t>
-        </is>
-      </c>
+          <t>のる</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>0.03278136981745161</v>
+        <v>0.2154543746036106</v>
       </c>
     </row>
     <row r="62">
@@ -5274,21 +5270,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>助け</t>
+          <t>身</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>たすけ</t>
+          <t>み</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>帮助；救助</t>
+          <t>身体；自身</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8964335804972258</v>
+        <v>0.5248279715561013</v>
       </c>
     </row>
     <row r="63">
@@ -5297,21 +5293,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>終わる</t>
+          <t>つける</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>おわる</t>
+          <t>つける</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>结束；完成</t>
+          <t>附着上</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.5583995982419308</v>
+        <v>0.7296082061332112</v>
       </c>
     </row>
     <row r="64">
@@ -5320,17 +5316,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>依頼</t>
+          <t>含む</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>いらい</t>
+          <t>ふくむ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>0.6995897513220604</v>
+        <v>0.1697849062598979</v>
       </c>
     </row>
     <row r="65">
@@ -5339,17 +5335,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>手段</t>
+          <t>依頼</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>しゅだん</t>
+          <t>いらい</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>0.27239181109788</v>
+        <v>0.6995897513220604</v>
       </c>
     </row>
     <row r="66">
@@ -5358,21 +5354,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>つく</t>
+          <t>手段</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>つく</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>附着</t>
-        </is>
-      </c>
+          <t>しゅだん</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>0.4699041995021516</v>
+        <v>0.27239181109788</v>
       </c>
     </row>
     <row r="67">
@@ -5381,17 +5373,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>含む</t>
+          <t>棘</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ふくむ</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>とげ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>刺；棘刺</t>
+        </is>
+      </c>
       <c r="E67" t="n">
-        <v>0.1697849062598979</v>
+        <v>0.8470719336040771</v>
       </c>
     </row>
     <row r="68">
@@ -5400,21 +5396,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>つける</t>
+          <t>終わる</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>つける</t>
+          <t>おわる</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>附着上</t>
+          <t>结束；完成</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.7296082061332112</v>
+        <v>0.5583995982419308</v>
       </c>
     </row>
     <row r="69">
@@ -5423,21 +5419,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>身</t>
+          <t>助け</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>み</t>
+          <t>たすけ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>身体；自身</t>
+          <t>帮助；救助</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.5248279715561013</v>
+        <v>0.8964335804972258</v>
       </c>
     </row>
     <row r="70">
@@ -5446,17 +5442,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>乗る</t>
+          <t>〜向けの</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>のる</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>むけの</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>面向…</t>
+        </is>
+      </c>
       <c r="E70" t="n">
-        <v>0.2154543746036106</v>
+        <v>0.03278136981745161</v>
       </c>
     </row>
     <row r="71">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>確保</t>
+          <t>歩く</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> かくほ</t>
+          <t>あるく</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0.5869566020980956</v>
+        <v>0.3094299906015364</v>
       </c>
     </row>
     <row r="72">
@@ -5503,21 +5503,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>棘</t>
+          <t>付く</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>とげ</t>
+          <t>つく</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>刺；棘刺</t>
+          <t>附着；跟随；附带</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.8470719336040771</v>
+        <v>0.6222028908725258</v>
       </c>
     </row>
     <row r="74">
@@ -5564,21 +5564,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>付く</t>
+          <t>遠い</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>つく</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>附着；跟随；附带</t>
-        </is>
-      </c>
+          <t>とおい</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.6222028908725258</v>
+        <v>0.0804643004661344</v>
       </c>
     </row>
     <row r="77">
@@ -5587,17 +5583,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>遠い</t>
+          <t>種</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>とおい</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>たね</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>种子</t>
+        </is>
+      </c>
       <c r="E77" t="n">
-        <v>0.0804643004661344</v>
+        <v>0.5799846764492018</v>
       </c>
     </row>
     <row r="78">
@@ -5606,21 +5606,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>種</t>
+          <t>大会</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>たね</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>种子</t>
-        </is>
-      </c>
+          <t>たいかい</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>0.5799846764492018</v>
+        <v>0.5962623031213689</v>
       </c>
     </row>
     <row r="79">
@@ -5629,17 +5625,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>大会</t>
+          <t>周辺</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>たいかい</t>
+          <t>しゅうへん</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>0.5962623031213689</v>
+        <v>0.6240224802069794</v>
       </c>
     </row>
     <row r="80">
@@ -5648,17 +5644,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>周辺</t>
+          <t>いくらでも</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>しゅうへん</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>いくらでも</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>很多，比比皆是</t>
+        </is>
+      </c>
       <c r="E80" t="n">
-        <v>0.6240224802069794</v>
+        <v>0.2423566077973657</v>
       </c>
     </row>
     <row r="81">
@@ -5667,21 +5667,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>いくらでも</t>
+          <t>主に</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>いくらでも</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>很多，比比皆是</t>
-        </is>
-      </c>
+          <t>おもに</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>0.2423566077973657</v>
+        <v>0.7384931277816161</v>
       </c>
     </row>
     <row r="82">
@@ -5690,17 +5686,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>主に</t>
+          <t>喜ぶ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>おもに</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>よろこぶ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>高兴；喜悦</t>
+        </is>
+      </c>
       <c r="E82" t="n">
-        <v>0.7384931277816161</v>
+        <v>0.1605515132678091</v>
       </c>
     </row>
     <row r="83">
@@ -5709,21 +5709,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>喜ぶ</t>
+          <t>妻</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>よろこぶ</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>高兴；喜悦</t>
-        </is>
-      </c>
+          <t>つま</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.1605515132678091</v>
+        <v>0.4598296493595505</v>
       </c>
     </row>
     <row r="84">
@@ -5732,17 +5728,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>妻</t>
+          <t>歳</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>つま</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>とし</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>年龄；年岁</t>
+        </is>
+      </c>
       <c r="E84" t="n">
-        <v>0.4598296493595505</v>
+        <v>0.5010015293573693</v>
       </c>
     </row>
     <row r="85">
@@ -5751,21 +5751,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>歳</t>
+          <t>に関する</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>とし</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>年龄；年岁</t>
-        </is>
-      </c>
+          <t>にかんする</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.5010015293573693</v>
+        <v>0.9759505034975631</v>
       </c>
     </row>
     <row r="86">
@@ -5820,17 +5816,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>に関する</t>
+          <t>野原</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>にかんする</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>のはら</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>地名</t>
+        </is>
+      </c>
       <c r="E88" t="n">
-        <v>0.9759505034975631</v>
+        <v>0.3133970434136019</v>
       </c>
     </row>
     <row r="89">
@@ -5839,21 +5839,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>車両</t>
+          <t>仲間</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>しゃりょう</t>
+          <t>なかま</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>车辆</t>
+          <t>同伴；伙伴</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.7132393243613997</v>
+        <v>0.5916809050701822</v>
       </c>
     </row>
     <row r="90">
@@ -5881,21 +5881,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>みたいだ</t>
+          <t>なんて言うか</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>みたいだ</t>
+          <t>なんていうか</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>好像；似乎</t>
+          <t>怎么说呢</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.3076875875133142</v>
+        <v>0.3507084647195219</v>
       </c>
     </row>
     <row r="92">
@@ -5904,17 +5904,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>以前</t>
+          <t>心</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>いぜん</t>
+          <t>こころ</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>0.137750143853302</v>
+        <v>0.663862044312855</v>
       </c>
     </row>
     <row r="93">
@@ -5923,17 +5923,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>火事</t>
+          <t>それ以上</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>かじ</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>それ以上</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>超过；再以上</t>
+        </is>
+      </c>
       <c r="E93" t="n">
-        <v>0.1277154205643206</v>
+        <v>0.2127272981679954</v>
       </c>
     </row>
     <row r="94">
@@ -5942,17 +5946,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>家事</t>
+          <t>子</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>かじ</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>こ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>孩子</t>
+        </is>
+      </c>
       <c r="E94" t="n">
-        <v>0.8709061364233516</v>
+        <v>0.1381464633146111</v>
       </c>
     </row>
     <row r="95">
@@ -5961,21 +5969,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>慣れる</t>
+          <t>歩行者</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>なれる</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>习惯；适应；熟练</t>
-        </is>
-      </c>
+          <t>ほこうしゃ</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.03553358612502477</v>
+        <v>0.2819027038116696</v>
       </c>
     </row>
     <row r="96">
@@ -5984,17 +5988,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>発表会</t>
+          <t>慣れる</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> はっぴょうかい</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>なれる</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>习惯；适应；熟练</t>
+        </is>
+      </c>
       <c r="E96" t="n">
-        <v>0.2479126428916648</v>
+        <v>0.03553358612502477</v>
       </c>
     </row>
     <row r="97">
@@ -6003,21 +6011,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>なんて言うか</t>
+          <t>発表会</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>なんていうか</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>怎么说呢</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> はっぴょうかい</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>0.3507084647195219</v>
+        <v>0.2479126428916648</v>
       </c>
     </row>
     <row r="98">
@@ -6026,17 +6030,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>歩行者</t>
+          <t>掛かる</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ほこうしゃ</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>かかる</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>悬挂；花费；需要</t>
+        </is>
+      </c>
       <c r="E98" t="n">
-        <v>0.2819027038116696</v>
+        <v>0.2148748467910445</v>
       </c>
     </row>
     <row r="99">
@@ -6045,21 +6053,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>子</t>
+          <t>家事</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>こ</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>孩子</t>
-        </is>
-      </c>
+          <t>かじ</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>0.1381464633146111</v>
+        <v>0.8709061364233516</v>
       </c>
     </row>
     <row r="100">
@@ -6068,21 +6072,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>それ以上</t>
+          <t>火事</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>それ以上</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>超过；再以上</t>
-        </is>
-      </c>
+          <t>かじ</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>0.2127272981679954</v>
+        <v>0.1277154205643206</v>
       </c>
     </row>
     <row r="101">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>心</t>
+          <t>以前</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>こころ</t>
+          <t>いぜん</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>0.663862044312855</v>
+        <v>0.137750143853302</v>
       </c>
     </row>
     <row r="102">
@@ -6110,21 +6110,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>野原</t>
+          <t>みたいだ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>のはら</t>
+          <t>みたいだ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>地名</t>
+          <t>好像；似乎</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.3133970434136019</v>
+        <v>0.3076875875133142</v>
       </c>
     </row>
     <row r="103">
@@ -6152,21 +6152,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>掛かる</t>
+          <t>橋</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>かかる</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>悬挂；花费；需要</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> はし</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>0.2148748467910445</v>
+        <v>0.95312324716926</v>
       </c>
     </row>
     <row r="105">
@@ -6217,17 +6213,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>橋</t>
+          <t>意見</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> はし</t>
+          <t>いけん</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>0.95312324716926</v>
+        <v>0.5977067524078469</v>
       </c>
     </row>
     <row r="108">
@@ -6236,17 +6232,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>意見</t>
+          <t>施設</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>いけん</t>
+          <t>しせつ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>0.5977067524078469</v>
+        <v>0.3669403285964704</v>
       </c>
     </row>
     <row r="109">
@@ -6255,17 +6251,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>施設</t>
+          <t>春</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>しせつ</t>
+          <t>はる</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>0.3669403285964704</v>
+        <v>0.9335943724101641</v>
       </c>
     </row>
     <row r="110">
@@ -6274,17 +6270,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>春</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>はる</t>
+          <t>ひつよう</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>0.9335943724101641</v>
+        <v>0.735277373609446</v>
       </c>
     </row>
     <row r="111">
@@ -6293,17 +6289,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>迎え</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ひつよう</t>
+          <t>むかえ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.735277373609446</v>
+        <v>0.00278341948611105</v>
       </c>
     </row>
     <row r="112">
@@ -6312,17 +6308,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>迎え</t>
+          <t>5年後</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>むかえ</t>
+          <t>ごねんご</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>0.00278341948611105</v>
+        <v>0.9987071055864212</v>
       </c>
     </row>
     <row r="113">
@@ -6331,17 +6327,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5年後</t>
+          <t>議員</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ごねんご</t>
+          <t>ぎいん</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>0.9987071055864212</v>
+        <v>0.1364918886804122</v>
       </c>
     </row>
     <row r="114">
@@ -6350,17 +6346,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>議員</t>
+          <t>出張</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ぎいん</t>
+          <t>しゅっちょう</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>0.1364918886804122</v>
+        <v>0.5642249569150684</v>
       </c>
     </row>
     <row r="115">
@@ -6369,17 +6365,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>出張</t>
+          <t>一人暮らし</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>しゅっちょう</t>
+          <t>ひとりぐらし</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>0.5642249569150684</v>
+        <v>0.7083872779064884</v>
       </c>
     </row>
     <row r="116">
@@ -6388,17 +6384,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>一人暮らし</t>
+          <t>車両</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ひとりぐらし</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>しゃりょう</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>车辆</t>
+        </is>
+      </c>
       <c r="E116" t="n">
-        <v>0.7083872779064884</v>
+        <v>0.7132393243613997</v>
       </c>
     </row>
     <row r="117">
